--- a/well_economics_NPV_IRR.xlsx.xlsx
+++ b/well_economics_NPV_IRR.xlsx.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A007E6F9-08AC-44B1-B7FF-EC9BEB3064A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BF6E87F-626E-46D8-9793-2B0E609154D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -612,7 +612,7 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>-2500000</c:v>
+                  <c:v>-7000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>884624.55029166432</c:v>
@@ -2117,7 +2117,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="5">
-        <v>2500000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2178,7 +2178,7 @@
   <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="I2" s="11">
         <f>IF(A2=0,-Inputs!$B$3,G2-H2)</f>
-        <v>-2500000</v>
+        <v>-7000000</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -4418,8 +4418,8 @@
         <v>32</v>
       </c>
       <c r="B65" s="13">
-        <f>NPV(Inputs!$B$9,I3:I62)+I2</f>
-        <v>4334128.1174720423</v>
+        <f>NPV(Inputs!$B$9/12, I3:I62)+I2</f>
+        <v>13993995.596086141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -4427,8 +4427,8 @@
         <v>33</v>
       </c>
       <c r="B66" s="14">
-        <f>IRR(I2:I62)*12</f>
-        <v>3.8948761172785948</v>
+        <f>(1+IRR(I2:I62))^12-1</f>
+        <v>2.034518065106496</v>
       </c>
     </row>
   </sheetData>
